--- a/artfynd/A 28936-2026 artfynd.xlsx
+++ b/artfynd/A 28936-2026 artfynd.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Moa Björnberg Dillner</t>
+          <t>Moa Björnberg Dillner, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>

--- a/artfynd/A 28936-2026 artfynd.xlsx
+++ b/artfynd/A 28936-2026 artfynd.xlsx
@@ -8753,7 +8753,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Philipp Weiss</t>
+          <t>Philipp Weiss, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>

--- a/artfynd/A 28936-2026 artfynd.xlsx
+++ b/artfynd/A 28936-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022132</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929389</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929390</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929391</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929395</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929396</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1645,6 +1690,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929398</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929400</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945955</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945963</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945978</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945983</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2287,6 +2362,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945985</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2394,6 +2474,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929387</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2501,6 +2586,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929397</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2613,6 +2703,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022137</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945967</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945976</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945969</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3046,6 +3156,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022126</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3153,6 +3268,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929382</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3260,6 +3380,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929383</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3367,6 +3492,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929385</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3474,6 +3604,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945947</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3581,6 +3716,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945948</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3688,6 +3828,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945953</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3795,6 +3940,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945960</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3902,6 +4052,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945962</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4009,6 +4164,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945970</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4116,6 +4276,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945991</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4223,6 +4388,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929394</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4330,6 +4500,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945949</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4442,6 +4617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022135</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4549,6 +4729,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946004</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4661,6 +4846,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022133</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4773,6 +4963,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022136</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4880,6 +5075,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945975</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4987,6 +5187,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946001</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5094,6 +5299,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946002</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5201,6 +5411,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946003</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5308,6 +5523,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946007</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5420,6 +5640,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022129</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5527,6 +5752,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945968</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5634,6 +5864,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945993</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5746,6 +5981,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022138</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5853,6 +6093,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929392</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5965,6 +6210,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945972</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6077,6 +6327,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945982</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6184,6 +6439,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945980</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6291,6 +6551,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945950</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6398,6 +6663,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945951</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6505,6 +6775,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945986</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6612,6 +6887,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945992</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6719,6 +6999,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929384</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6826,6 +7111,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945957</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6933,6 +7223,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945958</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7040,6 +7335,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945990</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7147,6 +7447,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945952</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7254,6 +7559,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945956</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7361,6 +7671,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945961</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7468,6 +7783,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945965</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7575,6 +7895,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945966</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7682,6 +8007,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945971</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7789,6 +8119,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945979</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7896,6 +8231,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945988</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8003,6 +8343,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945989</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8110,6 +8455,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945994</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8217,6 +8567,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945995</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8324,6 +8679,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929399</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8436,6 +8796,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022134</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8543,6 +8908,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946005</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8650,6 +9020,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946006</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8757,6 +9132,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945937</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8864,6 +9244,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945946</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8971,6 +9356,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946010</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9078,6 +9468,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945936</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9185,6 +9580,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946014</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9292,6 +9692,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946016</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9404,6 +9809,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022113</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9516,6 +9926,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022117</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9628,6 +10043,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022119</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9740,6 +10160,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022121</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9847,6 +10272,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929401</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9954,6 +10384,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929402</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10061,6 +10496,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945939</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10168,6 +10608,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946017</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10275,6 +10720,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946018</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10382,6 +10832,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946020</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10489,6 +10944,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946022</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10596,6 +11056,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945942</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10703,6 +11168,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945945</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10810,6 +11280,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946013</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10922,6 +11397,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022118</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11034,6 +11514,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022115</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11146,6 +11631,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022120</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11258,6 +11748,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022122</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11365,6 +11860,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929378</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11472,6 +11972,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929379</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11579,6 +12084,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945933</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11686,6 +12196,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945934</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11793,6 +12308,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945941</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11900,6 +12420,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945944</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12012,6 +12537,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022123</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12119,6 +12649,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929380</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12226,6 +12761,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929381</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12333,6 +12873,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945940</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12445,6 +12990,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022116</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12552,6 +13102,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134929377</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12659,6 +13214,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946009</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12766,6 +13326,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946012</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12878,6 +13443,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946011</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12990,6 +13560,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946023</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13102,6 +13677,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022114</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13209,6 +13789,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134945932</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13321,6 +13906,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131022124</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13428,6 +14018,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946008</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13535,8 +14130,134 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134946015</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28936-2026 artfynd.xlsx
+++ b/artfynd/A 28936-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>134929386</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>134929389</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>134929390</v>
       </c>
       <c r="B6" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>134929391</v>
       </c>
       <c r="B7" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>134929395</v>
       </c>
       <c r="B8" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>134929396</v>
       </c>
       <c r="B9" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>134929398</v>
       </c>
       <c r="B10" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>134929400</v>
       </c>
       <c r="B11" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>134945955</v>
       </c>
       <c r="B12" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>134945963</v>
       </c>
       <c r="B13" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>134945978</v>
       </c>
       <c r="B14" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>134945983</v>
       </c>
       <c r="B15" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>134945985</v>
       </c>
       <c r="B16" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>134929387</v>
       </c>
       <c r="B17" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>134929397</v>
       </c>
       <c r="B18" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>134945967</v>
       </c>
       <c r="B20" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>134945976</v>
       </c>
       <c r="B21" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>134945969</v>
       </c>
       <c r="B22" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>134929382</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>134929383</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>134929385</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>134945947</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>134945948</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>134945953</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>134945960</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>134945962</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>134945970</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>134945991</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>134929394</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         <v>134945949</v>
       </c>
       <c r="B35" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         <v>134946004</v>
       </c>
       <c r="B37" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>134945975</v>
       </c>
       <c r="B40" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>134946001</v>
       </c>
       <c r="B41" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134946002</v>
       </c>
       <c r="B42" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>134946003</v>
       </c>
       <c r="B43" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         <v>134946007</v>
       </c>
       <c r="B44" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>134945968</v>
       </c>
       <c r="B46" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>134945993</v>
       </c>
       <c r="B47" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5992,7 +5992,7 @@
         <v>134929392</v>
       </c>
       <c r="B49" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>134945972</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>134945982</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>134945980</v>
       </c>
       <c r="B52" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>134945950</v>
       </c>
       <c r="B53" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>134945951</v>
       </c>
       <c r="B54" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>134945986</v>
       </c>
       <c r="B55" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>134945992</v>
       </c>
       <c r="B56" t="n">
-        <v>109924</v>
+        <v>109980</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>134929384</v>
       </c>
       <c r="B57" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>134945957</v>
       </c>
       <c r="B58" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>134945958</v>
       </c>
       <c r="B59" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>134945990</v>
       </c>
       <c r="B60" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>134945952</v>
       </c>
       <c r="B61" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>134945956</v>
       </c>
       <c r="B62" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>134945961</v>
       </c>
       <c r="B63" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>134945965</v>
       </c>
       <c r="B64" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>134945966</v>
       </c>
       <c r="B65" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>134945971</v>
       </c>
       <c r="B66" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>134945979</v>
       </c>
       <c r="B67" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>134945988</v>
       </c>
       <c r="B68" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>134945989</v>
       </c>
       <c r="B69" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>134945994</v>
       </c>
       <c r="B70" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>134945995</v>
       </c>
       <c r="B71" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>134929399</v>
       </c>
       <c r="B72" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>134946005</v>
       </c>
       <c r="B74" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>134946006</v>
       </c>
       <c r="B75" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>134945937</v>
       </c>
       <c r="B76" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>134945946</v>
       </c>
       <c r="B77" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>134946010</v>
       </c>
       <c r="B78" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>134945936</v>
       </c>
       <c r="B79" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>134946014</v>
       </c>
       <c r="B80" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>134946016</v>
       </c>
       <c r="B81" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>134929401</v>
       </c>
       <c r="B86" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>134929402</v>
       </c>
       <c r="B87" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         <v>134945939</v>
       </c>
       <c r="B88" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10507,7 +10507,7 @@
         <v>134946017</v>
       </c>
       <c r="B89" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>134946018</v>
       </c>
       <c r="B90" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>134946020</v>
       </c>
       <c r="B91" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>134946022</v>
       </c>
       <c r="B92" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>134945942</v>
       </c>
       <c r="B93" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>134945945</v>
       </c>
       <c r="B94" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>134946013</v>
       </c>
       <c r="B95" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>134929378</v>
       </c>
       <c r="B100" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>134929379</v>
       </c>
       <c r="B101" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>134945933</v>
       </c>
       <c r="B102" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>134945934</v>
       </c>
       <c r="B103" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>134945941</v>
       </c>
       <c r="B104" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>134945944</v>
       </c>
       <c r="B105" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>134929380</v>
       </c>
       <c r="B107" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>134929381</v>
       </c>
       <c r="B108" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>134945940</v>
       </c>
       <c r="B109" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>134929377</v>
       </c>
       <c r="B111" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>134946009</v>
       </c>
       <c r="B112" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>134946012</v>
       </c>
       <c r="B113" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>134946011</v>
       </c>
       <c r="B114" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>134946023</v>
       </c>
       <c r="B115" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>134945932</v>
       </c>
       <c r="B117" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>134946008</v>
       </c>
       <c r="B119" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>134946015</v>
       </c>
       <c r="B120" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
